--- a/Result/blind_sequencing_result_line_version_length3.xlsx
+++ b/Result/blind_sequencing_result_line_version_length3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rt753149/Desktop/mRNA_sequencing/Result/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shangsilin/Desktop/Autumn 2025/mRNA_sequencing/Result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20F2EE9-311E-164D-A279-2E5F2B53FDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F9E246-22BE-F948-B7E6-F70E0B428F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <si>
     <t>sequence</t>
   </si>
@@ -711,13 +711,46 @@
   </si>
   <si>
     <t>ladder111</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>UGGUGGUGGUGG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>UGGUGGUGGUGG</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -732,6 +765,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1063,13 +1101,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="45.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,7 +1122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1097,7 +1136,7 @@
         <v>16505.069796940599</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1110,8 +1149,11 @@
       <c r="D3">
         <v>14257.868563919201</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1166,11 @@
       <c r="D4">
         <v>13972.646853170399</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1139,7 +1184,7 @@
         <v>3952.57866528776</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1153,7 +1198,7 @@
         <v>10754.342233007799</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1167,7 +1212,7 @@
         <v>9029.2015861727796</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1181,7 +1226,7 @@
         <v>692.11172389375804</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1195,7 +1240,7 @@
         <v>1688.2303360020901</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -1209,7 +1254,7 @@
         <v>982.13993892105498</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1223,7 +1268,7 @@
         <v>634.09451289021501</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1237,7 +1282,7 @@
         <v>1570.1798560007901</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1251,7 +1296,7 @@
         <v>981.15706695734502</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1265,7 +1310,7 @@
         <v>1005.16858172743</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1279,7 +1324,7 @@
         <v>635.08169443631402</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>32</v>
       </c>
